--- a/projects/huudi/create_account_cases.xlsx
+++ b/projects/huudi/create_account_cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>huudi_001</t>
+          <t>huudi_reg_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open createAccount page</t>
+          <t>register create account</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -484,7 +484,191 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>huudi_reg_01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>register create account</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>input[name=firstName]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TestFirst</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>huudi_reg_01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>register create account</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>input[name=lastName]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TestLast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>huudi_reg_01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>register create account</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>input[name=email]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>test@example.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>huudi_reg_01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>register create account</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>input[name=password]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Test@1234</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>huudi_reg_01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>register create account</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>input[name=confirmPassword]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Test@1234</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>huudi_reg_01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>register create account</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>click</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>button:has-text("Next")</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
